--- a/polls/013_municipal_policy_public_opinion_survey_form--polls.xlsx
+++ b/polls/013_municipal_policy_public_opinion_survey_form--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'area_1',_'label':_'area_1'}</t>
+          <t>area_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Area 1', 'label': 'Area 1'}</t>
+          <t>Area 1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'area_2',_'label':_'area_2'}</t>
+          <t>area_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Area 2', 'label': 'Area 2'}</t>
+          <t>Area 2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'area_3',_'label':_'area_3'}</t>
+          <t>area_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Area 3', 'label': 'Area 3'}</t>
+          <t>Area 3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'area_4',_'label':_'area_4'}</t>
+          <t>area_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Area 4', 'label': 'Area 4'}</t>
+          <t>Area 4</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'area_5',_'label':_'area_5'}</t>
+          <t>area_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Area 5', 'label': 'Area 5'}</t>
+          <t>Area 5</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'area_6',_'label':_'area_6'}</t>
+          <t>area_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Area 6', 'label': 'Area 6'}</t>
+          <t>Area 6</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'area_7',_'label':_'area_7'}</t>
+          <t>area_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Area 7', 'label': 'Area 7'}</t>
+          <t>Area 7</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'area_8',_'label':_'area_8'}</t>
+          <t>area_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Area 8', 'label': 'Area 8'}</t>
+          <t>Area 8</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'city_council_1',_'label':_'city_council_1'}</t>
+          <t>city_council_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'City Council 1', 'label': 'City Council 1'}</t>
+          <t>City Council 1</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'city_council_2',_'label':_'city_council_2'}</t>
+          <t>city_council_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'City Council 2', 'label': 'City Council 2'}</t>
+          <t>City Council 2</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'city_council_3',_'label':_'city_council_3'}</t>
+          <t>city_council_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'City Council 3', 'label': 'City Council 3'}</t>
+          <t>City Council 3</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'spring',_'label':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Spring', 'label': 'Spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'summer',_'label':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Summer', 'label': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'autumn',_'label':_'autumn'}</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Autumn', 'label': 'Autumn'}</t>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'winter',_'label':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Winter', 'label': 'Winter'}</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'owns',_'label':_'owns'}</t>
+          <t>owns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Owns', 'label': 'Owns'}</t>
+          <t>Owns</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'rents',_'label':_'rents'}</t>
+          <t>rents</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Rents', 'label': 'Rents'}</t>
+          <t>Rents</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
